--- a/각 파일 경로.xlsx
+++ b/각 파일 경로.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jinpyo\AppData\Local\nvim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8A8A8E-AEB3-4ECF-9989-46A559996B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225320E3-79FD-4F4C-95D4-960347A14090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>이클립스 설정</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -104,6 +104,14 @@
   </si>
   <si>
     <t>C:\MyProgramFiles\msys64\home\jinpyo\.tmux.conf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-&gt; C:\Users\jinpyo\AppData\Local\nvim\tmux\</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-&gt; C:\Users\jinpyo\AppData\Local\nvim\wezterm\</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -507,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C39"/>
+  <dimension ref="B1:C40"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.4">
@@ -590,6 +598,11 @@
         <v>13</v>
       </c>
     </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B36" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B37" s="4"/>
     </row>
@@ -601,6 +614,11 @@
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B39" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B40" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/각 파일 경로.xlsx
+++ b/각 파일 경로.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jinpyo\AppData\Local\nvim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225320E3-79FD-4F4C-95D4-960347A14090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2B48A5-A808-4FA6-8B92-5DCC9E16076F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>이클립스 설정</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -112,6 +112,24 @@
   </si>
   <si>
     <t>-&gt; C:\Users\jinpyo\AppData\Local\nvim\wezterm\</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qutebrowser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:\Users\jinpyo\AppData\Roaming\qutebrowser\config\</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C:\Users\jinpyo\AppData\Local\nvim\util\browser\userscripts\</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>New-Item -ItemType SymbolicLink `
+  -Path "C:\Users\jinpyo\AppData\Roaming\qutebrowser\config\userscripts" `
+  -Target "C:\Users\jinpyo\AppData\Local\nvim\util\browser\userscripts"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -177,13 +195,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -213,8 +234,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>143756</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>259370</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>175</xdr:rowOff>
     </xdr:to>
@@ -515,8 +536,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C40"/>
+  <dimension ref="B1:C48"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="33.796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
@@ -619,6 +643,26 @@
     <row r="40" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B40" s="1" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B45" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="B48" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
